--- a/online-kalkulator-print-addon/Template.xlsx
+++ b/online-kalkulator-print-addon/Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="DieseArbeitsmappe"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scherzer Thomas\Documents\GitHub\hassio-addons\online-kalkulator-print-addon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AD5229-1374-4035-8164-FFB82F3F12C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3A1188-E210-4C36-B682-047F3EE7F3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="20715" windowHeight="13155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="46470" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arbeitsverfahren" sheetId="1" r:id="rId1"/>
@@ -228,12 +228,6 @@
     <t>3.</t>
   </si>
   <si>
-    <t>Wagnis für Risiko/Gewährleistung</t>
-  </si>
-  <si>
-    <t>Leistungseinheiten Bandbreite (Einheiten/Stunde)</t>
-  </si>
-  <si>
     <t>Leistungspreis</t>
   </si>
   <si>
@@ -261,15 +255,9 @@
     <t>Anschaffungspreis (AP)</t>
   </si>
   <si>
-    <t>Nebenzeiten</t>
-  </si>
-  <si>
     <t>b) Zuschlag für Nebenzeiten - Grundmaschine</t>
   </si>
   <si>
-    <t>Summe Zuschläge für Nebenzeiten</t>
-  </si>
-  <si>
     <t>a) Zuschlag für Nebenzeiten - Personal</t>
   </si>
   <si>
@@ -285,9 +273,6 @@
     <t>Organisations- und Unternehmenskosten (Basis: 1+2+3)</t>
   </si>
   <si>
-    <t>Wagnis für Risiko/Gewährleistung (Basis: 1+2+3)</t>
-  </si>
-  <si>
     <t>Kreiselegge 3m</t>
   </si>
   <si>
@@ -301,6 +286,21 @@
   </si>
   <si>
     <t xml:space="preserve">Reparaturkosten (in % vom AP/100h) </t>
+  </si>
+  <si>
+    <t>Kosten für Nebenzeiten</t>
+  </si>
+  <si>
+    <t>Summe Kosten für Nebenzeiten</t>
+  </si>
+  <si>
+    <t>Kosten für Wagnis/Gewährleistung/Gewinn</t>
+  </si>
+  <si>
+    <t>Wagnis für Wagnis/Gewährleistung/Gewinn (Basis: 1+2+3)</t>
+  </si>
+  <si>
+    <t>Bandbreite für Leistungseinheiten (Einheiten/Std.)</t>
   </si>
 </sst>
 </file>
@@ -977,10 +977,10 @@
   <cols>
     <col min="1" max="1" width="5.1328125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.46484375" customWidth="1"/>
-    <col min="3" max="3" width="12.265625" customWidth="1"/>
-    <col min="4" max="4" width="12.265625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.265625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.265625" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.3984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -1001,7 +1001,7 @@
       <c r="C3" s="31"/>
       <c r="D3" s="86">
         <f ca="1">TODAY()</f>
-        <v>46038</v>
+        <v>46054</v>
       </c>
       <c r="E3" s="31" t="s">
         <v>9</v>
@@ -1023,7 +1023,7 @@
     <row r="5" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A5" s="88"/>
       <c r="B5" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C5" s="19"/>
       <c r="D5" s="20">
@@ -1097,7 +1097,7 @@
         <v>13</v>
       </c>
       <c r="C10" s="105" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D10" s="105"/>
       <c r="E10" s="105"/>
@@ -1109,7 +1109,7 @@
         <v/>
       </c>
       <c r="B11" s="33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" s="33"/>
       <c r="D11" s="34">
@@ -1207,7 +1207,7 @@
         <v/>
       </c>
       <c r="B17" s="44" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C17" s="44"/>
       <c r="D17" s="45">
@@ -1843,7 +1843,7 @@
     <row r="51" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A51" s="68"/>
       <c r="B51" s="19" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C51" s="27">
         <v>15</v>
@@ -1862,7 +1862,7 @@
     <row r="52" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A52" s="68"/>
       <c r="B52" s="19" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C52" s="27">
         <v>0.2</v>
@@ -1881,7 +1881,7 @@
     <row r="53" spans="1:6" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A53" s="68"/>
       <c r="B53" s="19" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C53" s="29">
         <v>0.7</v>
@@ -1954,7 +1954,7 @@
         <v/>
       </c>
       <c r="B57" s="33" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C57" s="41">
         <v>0</v>
@@ -1976,7 +1976,7 @@
         <v/>
       </c>
       <c r="B58" s="33" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C58" s="41">
         <v>0.2</v>
@@ -1998,7 +1998,7 @@
         <v/>
       </c>
       <c r="B59" s="33" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C59" s="42">
         <v>0.7</v>
@@ -2077,7 +2077,7 @@
         <v/>
       </c>
       <c r="B63" s="44" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C63" s="52">
         <v>0</v>
@@ -2099,7 +2099,7 @@
         <v/>
       </c>
       <c r="B64" s="44" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C64" s="52">
         <v>0.2</v>
@@ -2121,7 +2121,7 @@
         <v/>
       </c>
       <c r="B65" s="44" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C65" s="54">
         <v>0.7</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="69" spans="1:6" s="4" customFormat="1" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="67" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B69" s="30" t="s">
         <v>35</v>
@@ -2242,13 +2242,13 @@
         <v>5</v>
       </c>
       <c r="B73" s="56" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C73" s="96" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D73" s="96" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E73" s="96" t="s">
         <v>25</v>
@@ -2258,7 +2258,7 @@
     <row r="74" spans="1:6" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A74" s="7"/>
       <c r="B74" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C74" s="89">
         <f>1/(1+GK_NebenzeitenPersonal)</f>
@@ -2278,7 +2278,7 @@
     <row r="75" spans="1:6" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A75" s="7"/>
       <c r="B75" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C75" s="89">
         <f>1/(1+GK_NebenzeitenGrundmaschine)</f>
@@ -2298,7 +2298,7 @@
     <row r="76" spans="1:6" s="3" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="55"/>
       <c r="B76" s="55" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C76" s="55"/>
       <c r="D76" s="74"/>
@@ -2323,11 +2323,11 @@
         <v>6</v>
       </c>
       <c r="B78" s="61" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C78" s="62"/>
       <c r="D78" s="97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E78" s="98" t="s">
         <v>25</v>
@@ -2337,7 +2337,7 @@
     <row r="79" spans="1:6" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A79" s="62"/>
       <c r="B79" s="65" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C79" s="65"/>
       <c r="D79" s="66">
@@ -2362,11 +2362,11 @@
         <v>7</v>
       </c>
       <c r="B81" s="69" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="C81" s="65"/>
       <c r="D81" s="97" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E81" s="98" t="s">
         <v>25</v>
@@ -2376,7 +2376,7 @@
     <row r="82" spans="1:6" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A82" s="62"/>
       <c r="B82" s="65" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C82" s="65"/>
       <c r="D82" s="66">
@@ -2400,7 +2400,7 @@
     </row>
     <row r="84" spans="1:6" s="4" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="70" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B84" s="71" t="s">
         <v>37</v>
@@ -2422,28 +2422,28 @@
     </row>
     <row r="86" spans="1:6" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A86" s="70" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" s="71" t="s">
+        <v>47</v>
+      </c>
+      <c r="C86" s="99" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" s="100" t="s">
+        <v>45</v>
+      </c>
+      <c r="E86" s="101" t="s">
+        <v>46</v>
+      </c>
+      <c r="F86" s="101" t="s">
         <v>59</v>
-      </c>
-      <c r="B86" s="71" t="s">
-        <v>49</v>
-      </c>
-      <c r="C86" s="99" t="s">
-        <v>46</v>
-      </c>
-      <c r="D86" s="100" t="s">
-        <v>47</v>
-      </c>
-      <c r="E86" s="101" t="s">
-        <v>48</v>
-      </c>
-      <c r="F86" s="101" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="87" spans="1:6" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A87" s="76"/>
       <c r="B87" s="73" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="C87" s="77">
         <v>0.8</v>
@@ -2463,7 +2463,7 @@
     <row r="88" spans="1:6" s="4" customFormat="1" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="70"/>
       <c r="B88" s="71" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C88" s="83">
         <f>$E$84/C87</f>
@@ -2504,19 +2504,20 @@
     <mergeCell ref="C56:F56"/>
   </mergeCells>
   <conditionalFormatting sqref="A22:E22 A23:F88">
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>CELL("Schutz",A22)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:F21">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>CELL("Schutz",A1)=0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="88" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LSeite &amp;P/&amp;N&amp;Cwww.online-kalkulator.at&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;C© HELSCH-Beratung im Ländlichen Raum, Pummerinplatz 2, 4490 St. Florian, T: +43 676 3112260, E: scherzer@helsch.at</oddFooter>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="48" max="16383" man="1"/>

--- a/online-kalkulator-print-addon/Template.xlsx
+++ b/online-kalkulator-print-addon/Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Scherzer Thomas\Documents\GitHub\hassio-addons\online-kalkulator-print-addon\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A3A1188-E210-4C36-B682-047F3EE7F3D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73922BE0-863F-41B4-B676-1A304F68D4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="46470" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27250" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arbeitsverfahren" sheetId="1" r:id="rId1"/>
@@ -297,10 +297,10 @@
     <t>Kosten für Wagnis/Gewährleistung/Gewinn</t>
   </si>
   <si>
-    <t>Wagnis für Wagnis/Gewährleistung/Gewinn (Basis: 1+2+3)</t>
-  </si>
-  <si>
     <t>Bandbreite für Leistungseinheiten (Einheiten/Std.)</t>
+  </si>
+  <si>
+    <t>Kosten für Wagnis/Gewährleistung/Gewinn (Basis: 1+2+3)</t>
   </si>
 </sst>
 </file>
@@ -2376,7 +2376,7 @@
     <row r="82" spans="1:6" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A82" s="62"/>
       <c r="B82" s="65" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C82" s="65"/>
       <c r="D82" s="66">
@@ -2443,7 +2443,7 @@
     <row r="87" spans="1:6" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.5">
       <c r="A87" s="76"/>
       <c r="B87" s="73" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C87" s="77">
         <v>0.8</v>
